--- a/output/Data and Chart Outputs/slovenia_sistat_pumping_daily.xlsx
+++ b/output/Data and Chart Outputs/slovenia_sistat_pumping_daily.xlsx
@@ -156,7 +156,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Slovenia electricity used for pumped storage (SiStat annual statistic, daily shape from ENTSO-E) (to Sep/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Slovenia electricity used for pumped storage (SiStat annual statistic, daily shape from ENTSO-E) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -177,7 +178,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -192,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -657,7 +658,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 23:39 UTC; daily 2021-01-01 to 2026-10-02; SiStat years 1996-2025</t>
+          <t>2026-10-28 01:00 UTC; daily 2021-01-01 to 2026-10-27; SiStat years 1996-2025</t>
         </is>
       </c>
     </row>
@@ -672,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -863,7 +864,7 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>35.527</v>
+        <v>35.52699999999999</v>
       </c>
     </row>
     <row r="24">
@@ -879,7 +880,7 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>38.5136</v>
+        <v>38.51359999999999</v>
       </c>
     </row>
     <row r="26">
@@ -919,7 +920,7 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>37.50230000000001</v>
+        <v>37.5023</v>
       </c>
     </row>
     <row r="31">
@@ -959,7 +960,7 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>35.6541</v>
+        <v>35.65409999999999</v>
       </c>
     </row>
     <row r="36">
@@ -967,7 +968,7 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>34.90730000000001</v>
+        <v>34.90729999999999</v>
       </c>
     </row>
     <row r="37">
@@ -983,7 +984,7 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>34.2393</v>
+        <v>34.23929999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1063,7 +1064,7 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>38.2066</v>
+        <v>38.20660000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1103,7 +1104,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>37.7826</v>
+        <v>37.78260000000001</v>
       </c>
     </row>
     <row r="54">
@@ -1135,7 +1136,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>39.0541</v>
+        <v>39.05410000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1167,7 +1168,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>35.9792</v>
+        <v>35.97920000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1199,7 +1200,7 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>38.6638</v>
+        <v>38.66379999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1223,7 +1224,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>38.71680000000001</v>
+        <v>38.71679999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1240,6 +1241,14 @@
       </c>
       <c r="B70" t="n">
         <v>24.8669</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>21.3586</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2101"/>
+  <dimension ref="A1:C2126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24371,6 +24380,281 @@
         <v>440.6</v>
       </c>
       <c r="C2101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>1109.8</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>602.7</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>1202.4</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>1563.2</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>944.3</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>1561.2</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>1473.6</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>1251.8</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>1052.2</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>1666</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>1272.9</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>456.6</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>249.1</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>1179.5</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>1407.9</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>584.8</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>968.4</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>737.2</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>1087.3</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>364.7</v>
+      </c>
+      <c r="C2126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24385,51 +24669,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Gross production</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Pumped-storage production (gross)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Net production</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Used for pumped storage</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Losses in the network</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Final consumption</t>
         </is>
@@ -24437,869 +24721,788 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1996</v>
       </c>
       <c r="B2" t="n">
-        <v>1996</v>
-      </c>
-      <c r="C2" t="n">
         <v>12737</v>
       </c>
+      <c r="D2" t="n">
+        <v>11972</v>
+      </c>
       <c r="E2" t="n">
-        <v>11972</v>
+        <v>859</v>
       </c>
       <c r="F2" t="n">
-        <v>859</v>
-      </c>
-      <c r="G2" t="n">
         <v>2526</v>
       </c>
+      <c r="H2" t="n">
+        <v>723</v>
+      </c>
       <c r="I2" t="n">
-        <v>723</v>
-      </c>
-      <c r="J2" t="n">
         <v>9582</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="B3" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C3" t="n">
         <v>13178</v>
       </c>
+      <c r="D3" t="n">
+        <v>12349</v>
+      </c>
       <c r="E3" t="n">
-        <v>12349</v>
+        <v>825</v>
       </c>
       <c r="F3" t="n">
-        <v>825</v>
-      </c>
-      <c r="G3" t="n">
         <v>2521</v>
       </c>
+      <c r="H3" t="n">
+        <v>682</v>
+      </c>
       <c r="I3" t="n">
-        <v>682</v>
-      </c>
-      <c r="J3" t="n">
         <v>9971</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1998</v>
       </c>
       <c r="B4" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C4" t="n">
         <v>13705</v>
       </c>
+      <c r="D4" t="n">
+        <v>12855</v>
+      </c>
       <c r="E4" t="n">
-        <v>12855</v>
+        <v>715</v>
       </c>
       <c r="F4" t="n">
-        <v>715</v>
-      </c>
-      <c r="G4" t="n">
         <v>2609</v>
       </c>
+      <c r="H4" t="n">
+        <v>764</v>
+      </c>
       <c r="I4" t="n">
-        <v>764</v>
-      </c>
-      <c r="J4" t="n">
         <v>10197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1999</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C5" t="n">
         <v>13261</v>
       </c>
+      <c r="D5" t="n">
+        <v>12456</v>
+      </c>
       <c r="E5" t="n">
-        <v>12456</v>
+        <v>601</v>
       </c>
       <c r="F5" t="n">
-        <v>601</v>
-      </c>
-      <c r="G5" t="n">
         <v>1934</v>
       </c>
+      <c r="H5" t="n">
+        <v>691</v>
+      </c>
       <c r="I5" t="n">
-        <v>691</v>
-      </c>
-      <c r="J5" t="n">
         <v>10432</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="B6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C6" t="n">
         <v>13624</v>
       </c>
+      <c r="D6" t="n">
+        <v>12795</v>
+      </c>
       <c r="E6" t="n">
-        <v>12795</v>
+        <v>4232</v>
       </c>
       <c r="F6" t="n">
-        <v>4232</v>
-      </c>
-      <c r="G6" t="n">
         <v>5553</v>
       </c>
+      <c r="H6" t="n">
+        <v>811</v>
+      </c>
       <c r="I6" t="n">
-        <v>811</v>
-      </c>
-      <c r="J6" t="n">
         <v>10664</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>2001</v>
       </c>
       <c r="B7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C7" t="n">
         <v>14466</v>
       </c>
+      <c r="D7" t="n">
+        <v>13592</v>
+      </c>
       <c r="E7" t="n">
-        <v>13592</v>
+        <v>3154</v>
       </c>
       <c r="F7" t="n">
-        <v>3154</v>
-      </c>
-      <c r="G7" t="n">
         <v>4926</v>
       </c>
+      <c r="H7" t="n">
+        <v>729</v>
+      </c>
       <c r="I7" t="n">
-        <v>729</v>
-      </c>
-      <c r="J7" t="n">
         <v>11091</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>2002</v>
       </c>
       <c r="B8" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C8" t="n">
         <v>14600</v>
       </c>
+      <c r="D8" t="n">
+        <v>13693</v>
+      </c>
       <c r="E8" t="n">
-        <v>13693</v>
+        <v>3794</v>
       </c>
       <c r="F8" t="n">
-        <v>3794</v>
-      </c>
-      <c r="G8" t="n">
         <v>4928</v>
       </c>
+      <c r="H8" t="n">
+        <v>737</v>
+      </c>
       <c r="I8" t="n">
-        <v>737</v>
-      </c>
-      <c r="J8" t="n">
         <v>11823</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>2003</v>
       </c>
       <c r="B9" t="n">
-        <v>2003</v>
-      </c>
-      <c r="C9" t="n">
         <v>13821</v>
       </c>
+      <c r="D9" t="n">
+        <v>12895</v>
+      </c>
       <c r="E9" t="n">
-        <v>12895</v>
+        <v>5975</v>
       </c>
       <c r="F9" t="n">
-        <v>5975</v>
-      </c>
-      <c r="G9" t="n">
         <v>5811</v>
       </c>
+      <c r="H9" t="n">
+        <v>856</v>
+      </c>
       <c r="I9" t="n">
-        <v>856</v>
-      </c>
-      <c r="J9" t="n">
         <v>12204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>2004</v>
       </c>
       <c r="B10" t="n">
-        <v>2004</v>
-      </c>
-      <c r="C10" t="n">
         <v>15272</v>
       </c>
+      <c r="D10" t="n">
+        <v>14308</v>
+      </c>
       <c r="E10" t="n">
-        <v>14308</v>
+        <v>7433</v>
       </c>
       <c r="F10" t="n">
-        <v>7433</v>
-      </c>
-      <c r="G10" t="n">
         <v>8189</v>
       </c>
+      <c r="H10" t="n">
+        <v>873</v>
+      </c>
       <c r="I10" t="n">
-        <v>873</v>
-      </c>
-      <c r="J10" t="n">
         <v>12679</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>2005</v>
       </c>
       <c r="B11" t="n">
-        <v>2005</v>
-      </c>
-      <c r="C11" t="n">
         <v>15117</v>
       </c>
+      <c r="D11" t="n">
+        <v>14149</v>
+      </c>
       <c r="E11" t="n">
-        <v>14149</v>
+        <v>9342</v>
       </c>
       <c r="F11" t="n">
-        <v>9342</v>
-      </c>
-      <c r="G11" t="n">
         <v>9667</v>
       </c>
+      <c r="H11" t="n">
+        <v>952</v>
+      </c>
       <c r="I11" t="n">
-        <v>952</v>
-      </c>
-      <c r="J11" t="n">
         <v>12872</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>2006</v>
       </c>
       <c r="B12" t="n">
-        <v>2006</v>
-      </c>
-      <c r="C12" t="n">
         <v>15115</v>
       </c>
+      <c r="D12" t="n">
+        <v>14117</v>
+      </c>
       <c r="E12" t="n">
-        <v>14117</v>
+        <v>7706</v>
       </c>
       <c r="F12" t="n">
-        <v>7706</v>
-      </c>
-      <c r="G12" t="n">
         <v>7662</v>
       </c>
+      <c r="H12" t="n">
+        <v>863</v>
+      </c>
       <c r="I12" t="n">
-        <v>863</v>
-      </c>
-      <c r="J12" t="n">
         <v>13298</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>2007</v>
       </c>
       <c r="B13" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C13" t="n">
         <v>15043</v>
       </c>
+      <c r="D13" t="n">
+        <v>14044</v>
+      </c>
       <c r="E13" t="n">
-        <v>14044</v>
+        <v>6106</v>
       </c>
       <c r="F13" t="n">
-        <v>6106</v>
-      </c>
-      <c r="G13" t="n">
         <v>5877</v>
       </c>
+      <c r="H13" t="n">
+        <v>868</v>
+      </c>
       <c r="I13" t="n">
-        <v>868</v>
-      </c>
-      <c r="J13" t="n">
         <v>13405</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>2008</v>
       </c>
       <c r="B14" t="n">
-        <v>2008</v>
-      </c>
-      <c r="C14" t="n">
         <v>16398</v>
       </c>
+      <c r="D14" t="n">
+        <v>15357</v>
+      </c>
       <c r="E14" t="n">
-        <v>15357</v>
+        <v>6225</v>
       </c>
       <c r="F14" t="n">
-        <v>6225</v>
-      </c>
-      <c r="G14" t="n">
         <v>7824</v>
       </c>
+      <c r="H14" t="n">
+        <v>813</v>
+      </c>
       <c r="I14" t="n">
-        <v>813</v>
-      </c>
-      <c r="J14" t="n">
         <v>12945</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>2009</v>
       </c>
       <c r="B15" t="n">
-        <v>2009</v>
-      </c>
-      <c r="C15" t="n">
         <v>16403</v>
       </c>
+      <c r="D15" t="n">
+        <v>15375</v>
+      </c>
       <c r="E15" t="n">
-        <v>15375</v>
+        <v>7780</v>
       </c>
       <c r="F15" t="n">
-        <v>7780</v>
-      </c>
-      <c r="G15" t="n">
         <v>10839</v>
       </c>
+      <c r="H15" t="n">
+        <v>893</v>
+      </c>
       <c r="I15" t="n">
-        <v>893</v>
-      </c>
-      <c r="J15" t="n">
         <v>11423</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>2010</v>
       </c>
       <c r="B16" t="n">
-        <v>2010</v>
+        <v>16440</v>
       </c>
       <c r="C16" t="n">
-        <v>16440</v>
+        <v>185</v>
       </c>
       <c r="D16" t="n">
-        <v>185</v>
+        <v>15410</v>
       </c>
       <c r="E16" t="n">
-        <v>15410</v>
+        <v>8625</v>
       </c>
       <c r="F16" t="n">
-        <v>8625</v>
+        <v>10745</v>
       </c>
       <c r="G16" t="n">
-        <v>10745</v>
+        <v>245</v>
       </c>
       <c r="H16" t="n">
-        <v>245</v>
+        <v>982</v>
       </c>
       <c r="I16" t="n">
-        <v>982</v>
-      </c>
-      <c r="J16" t="n">
         <v>12063</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>2011</v>
       </c>
       <c r="B17" t="n">
-        <v>2011</v>
+        <v>16059</v>
       </c>
       <c r="C17" t="n">
-        <v>16059</v>
+        <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>144</v>
+        <v>15001</v>
       </c>
       <c r="E17" t="n">
-        <v>15001</v>
+        <v>7036</v>
       </c>
       <c r="F17" t="n">
-        <v>7036</v>
+        <v>8408</v>
       </c>
       <c r="G17" t="n">
-        <v>8408</v>
+        <v>193</v>
       </c>
       <c r="H17" t="n">
-        <v>193</v>
+        <v>824</v>
       </c>
       <c r="I17" t="n">
-        <v>824</v>
-      </c>
-      <c r="J17" t="n">
         <v>12612</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>2012</v>
       </c>
       <c r="B18" t="n">
-        <v>2012</v>
+        <v>15736</v>
       </c>
       <c r="C18" t="n">
-        <v>15736</v>
+        <v>188</v>
       </c>
       <c r="D18" t="n">
-        <v>188</v>
+        <v>14705</v>
       </c>
       <c r="E18" t="n">
-        <v>14705</v>
+        <v>7452</v>
       </c>
       <c r="F18" t="n">
-        <v>7452</v>
+        <v>8491</v>
       </c>
       <c r="G18" t="n">
-        <v>8491</v>
+        <v>251</v>
       </c>
       <c r="H18" t="n">
-        <v>251</v>
+        <v>875</v>
       </c>
       <c r="I18" t="n">
-        <v>875</v>
-      </c>
-      <c r="J18" t="n">
         <v>12540</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>2013</v>
       </c>
       <c r="B19" t="n">
-        <v>2013</v>
+        <v>16103</v>
       </c>
       <c r="C19" t="n">
-        <v>16103</v>
+        <v>294</v>
       </c>
       <c r="D19" t="n">
-        <v>294</v>
+        <v>15117</v>
       </c>
       <c r="E19" t="n">
-        <v>15117</v>
+        <v>7521</v>
       </c>
       <c r="F19" t="n">
-        <v>7521</v>
+        <v>8811</v>
       </c>
       <c r="G19" t="n">
-        <v>8811</v>
+        <v>392</v>
       </c>
       <c r="H19" t="n">
-        <v>392</v>
+        <v>848</v>
       </c>
       <c r="I19" t="n">
-        <v>848</v>
-      </c>
-      <c r="J19" t="n">
         <v>12587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>2014</v>
       </c>
       <c r="B20" t="n">
-        <v>2014</v>
+        <v>17437</v>
       </c>
       <c r="C20" t="n">
-        <v>17437</v>
+        <v>274</v>
       </c>
       <c r="D20" t="n">
-        <v>274</v>
+        <v>16486</v>
       </c>
       <c r="E20" t="n">
-        <v>16486</v>
+        <v>7254</v>
       </c>
       <c r="F20" t="n">
-        <v>7254</v>
+        <v>9997</v>
       </c>
       <c r="G20" t="n">
-        <v>9997</v>
+        <v>363</v>
       </c>
       <c r="H20" t="n">
-        <v>363</v>
+        <v>821</v>
       </c>
       <c r="I20" t="n">
-        <v>821</v>
-      </c>
-      <c r="J20" t="n">
         <v>12559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>2015</v>
       </c>
       <c r="B21" t="n">
-        <v>2015</v>
+        <v>15100</v>
       </c>
       <c r="C21" t="n">
-        <v>15100</v>
+        <v>283</v>
       </c>
       <c r="D21" t="n">
-        <v>283</v>
+        <v>14187</v>
       </c>
       <c r="E21" t="n">
-        <v>14187</v>
+        <v>9045</v>
       </c>
       <c r="F21" t="n">
-        <v>9045</v>
+        <v>9093</v>
       </c>
       <c r="G21" t="n">
-        <v>9093</v>
+        <v>380</v>
       </c>
       <c r="H21" t="n">
-        <v>380</v>
+        <v>864</v>
       </c>
       <c r="I21" t="n">
-        <v>864</v>
-      </c>
-      <c r="J21" t="n">
         <v>12895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>2016</v>
       </c>
       <c r="B22" t="n">
-        <v>2016</v>
+        <v>16500</v>
       </c>
       <c r="C22" t="n">
-        <v>16500</v>
+        <v>279</v>
       </c>
       <c r="D22" t="n">
-        <v>279</v>
+        <v>15546</v>
       </c>
       <c r="E22" t="n">
-        <v>15546</v>
+        <v>8359</v>
       </c>
       <c r="F22" t="n">
-        <v>8359</v>
+        <v>9535</v>
       </c>
       <c r="G22" t="n">
-        <v>9535</v>
+        <v>373</v>
       </c>
       <c r="H22" t="n">
-        <v>373</v>
+        <v>876</v>
       </c>
       <c r="I22" t="n">
-        <v>876</v>
-      </c>
-      <c r="J22" t="n">
         <v>13121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>2017</v>
       </c>
       <c r="B23" t="n">
-        <v>2017</v>
+        <v>16326.225</v>
       </c>
       <c r="C23" t="n">
-        <v>16326.225</v>
+        <v>272.575</v>
       </c>
       <c r="D23" t="n">
-        <v>272.575</v>
+        <v>15396.876</v>
       </c>
       <c r="E23" t="n">
-        <v>15396.876</v>
+        <v>9132.531999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>9132.531999999999</v>
+        <v>9648.191999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>9648.191999999999</v>
+        <v>365.3</v>
       </c>
       <c r="H23" t="n">
-        <v>365.3</v>
+        <v>893.29</v>
       </c>
       <c r="I23" t="n">
-        <v>893.29</v>
-      </c>
-      <c r="J23" t="n">
         <v>13622.625</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>2018</v>
       </c>
       <c r="B24" t="n">
-        <v>2018</v>
+        <v>16326.935</v>
       </c>
       <c r="C24" t="n">
-        <v>16326.935</v>
+        <v>188.673</v>
       </c>
       <c r="D24" t="n">
-        <v>188.673</v>
+        <v>15441.97</v>
       </c>
       <c r="E24" t="n">
-        <v>15441.97</v>
+        <v>8930.239</v>
       </c>
       <c r="F24" t="n">
-        <v>8930.239</v>
+        <v>9432.402</v>
       </c>
       <c r="G24" t="n">
-        <v>9432.402</v>
+        <v>252.438</v>
       </c>
       <c r="H24" t="n">
-        <v>252.438</v>
+        <v>879.694</v>
       </c>
       <c r="I24" t="n">
-        <v>879.694</v>
-      </c>
-      <c r="J24" t="n">
         <v>13807.675</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>2019</v>
       </c>
       <c r="B25" t="n">
-        <v>2019</v>
+        <v>16099.564</v>
       </c>
       <c r="C25" t="n">
-        <v>16099.564</v>
+        <v>203.143</v>
       </c>
       <c r="D25" t="n">
-        <v>203.143</v>
+        <v>15224.354</v>
       </c>
       <c r="E25" t="n">
-        <v>15224.354</v>
+        <v>9021.272999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>9021.272999999999</v>
+        <v>9339.829</v>
       </c>
       <c r="G25" t="n">
-        <v>9339.829</v>
+        <v>271.77</v>
       </c>
       <c r="H25" t="n">
-        <v>271.77</v>
+        <v>858.347</v>
       </c>
       <c r="I25" t="n">
-        <v>858.347</v>
-      </c>
-      <c r="J25" t="n">
         <v>13775.681</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>2020</v>
       </c>
       <c r="B26" t="n">
-        <v>2020</v>
+        <v>17190.698</v>
       </c>
       <c r="C26" t="n">
-        <v>17190.698</v>
+        <v>290.683</v>
       </c>
       <c r="D26" t="n">
-        <v>290.683</v>
+        <v>16289.674</v>
       </c>
       <c r="E26" t="n">
-        <v>16289.674</v>
+        <v>7119.95</v>
       </c>
       <c r="F26" t="n">
-        <v>7119.95</v>
+        <v>9123.056</v>
       </c>
       <c r="G26" t="n">
-        <v>9123.056</v>
+        <v>390.908</v>
       </c>
       <c r="H26" t="n">
-        <v>390.908</v>
+        <v>848.755</v>
       </c>
       <c r="I26" t="n">
-        <v>848.755</v>
-      </c>
-      <c r="J26" t="n">
         <v>13046.905</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>2021</v>
       </c>
       <c r="B27" t="n">
-        <v>2021</v>
+        <v>15876.922</v>
       </c>
       <c r="C27" t="n">
-        <v>15876.922</v>
+        <v>284.556</v>
       </c>
       <c r="D27" t="n">
-        <v>284.556</v>
+        <v>15048.057</v>
       </c>
       <c r="E27" t="n">
-        <v>15048.057</v>
+        <v>8387.153</v>
       </c>
       <c r="F27" t="n">
-        <v>8387.153</v>
+        <v>8657.572</v>
       </c>
       <c r="G27" t="n">
-        <v>8657.572</v>
+        <v>390.672</v>
       </c>
       <c r="H27" t="n">
-        <v>390.672</v>
+        <v>836.917</v>
       </c>
       <c r="I27" t="n">
-        <v>836.917</v>
-      </c>
-      <c r="J27" t="n">
         <v>13550.049</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>2022</v>
       </c>
       <c r="B28" t="n">
-        <v>2022</v>
+        <v>13615.509</v>
       </c>
       <c r="C28" t="n">
-        <v>13615.509</v>
+        <v>252.187</v>
       </c>
       <c r="D28" t="n">
-        <v>252.187</v>
+        <v>12867.636</v>
       </c>
       <c r="E28" t="n">
-        <v>12867.636</v>
+        <v>10198.242</v>
       </c>
       <c r="F28" t="n">
-        <v>10198.242</v>
+        <v>8752.325999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>8752.325999999999</v>
+        <v>340.527</v>
       </c>
       <c r="H28" t="n">
-        <v>340.527</v>
+        <v>845.318</v>
       </c>
       <c r="I28" t="n">
-        <v>845.318</v>
-      </c>
-      <c r="J28" t="n">
         <v>13127.707</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>2023</v>
       </c>
       <c r="B29" t="n">
-        <v>2023</v>
+        <v>15876.412</v>
       </c>
       <c r="C29" t="n">
-        <v>15876.412</v>
+        <v>301.301</v>
       </c>
       <c r="D29" t="n">
-        <v>301.301</v>
+        <v>15130.209</v>
       </c>
       <c r="E29" t="n">
-        <v>15130.209</v>
+        <v>9114.050999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>9114.050999999999</v>
+        <v>10619.838</v>
       </c>
       <c r="G29" t="n">
-        <v>10619.838</v>
+        <v>405.475</v>
       </c>
       <c r="H29" t="n">
-        <v>405.475</v>
+        <v>762.926</v>
       </c>
       <c r="I29" t="n">
-        <v>762.926</v>
-      </c>
-      <c r="J29" t="n">
         <v>12456.021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>16988.169</v>
       </c>
       <c r="C30" t="n">
-        <v>16988.169</v>
+        <v>283.039</v>
       </c>
       <c r="D30" t="n">
-        <v>283.039</v>
+        <v>16108.104</v>
       </c>
       <c r="E30" t="n">
-        <v>16108.104</v>
+        <v>9968.754999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>9968.754999999999</v>
+        <v>12374.696</v>
       </c>
       <c r="G30" t="n">
-        <v>12374.696</v>
+        <v>381.349</v>
       </c>
       <c r="H30" t="n">
-        <v>381.349</v>
+        <v>865.577</v>
       </c>
       <c r="I30" t="n">
-        <v>865.577</v>
-      </c>
-      <c r="J30" t="n">
         <v>12455.237</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>2025</v>
       </c>
       <c r="B31" t="n">
-        <v>2025</v>
+        <v>14963.26</v>
       </c>
       <c r="C31" t="n">
-        <v>15010.982</v>
+        <v>324.688</v>
       </c>
       <c r="D31" t="n">
-        <v>324.688</v>
+        <v>14320.197</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10321.652</v>
       </c>
       <c r="F31" t="n">
-        <v>10321.652</v>
+        <v>10813.46</v>
       </c>
       <c r="G31" t="n">
-        <v>10813.46</v>
+        <v>436.939</v>
       </c>
       <c r="H31" t="n">
-        <v>436.939</v>
+        <v>813.6609999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>12577.789</v>
       </c>
     </row>
   </sheetData>
